--- a/artfynd/A 44928-2022 artfynd.xlsx
+++ b/artfynd/A 44928-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44928-2022 artfynd.xlsx
+++ b/artfynd/A 44928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80107496</v>
+        <v>103912716</v>
       </c>
       <c r="B2" t="n">
-        <v>95990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221930</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väte, Skäldan, vägförgreningen 535 m SV, Rovalds 1:12 (2), Gtl</t>
+          <t>Hajdkvie Norr, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699433.9602591776</v>
+        <v>699332</v>
       </c>
       <c r="R2" t="n">
-        <v>6364033.843434261</v>
+        <v>6364080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,69 +756,73 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Michael Krikorev, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80107497</v>
+        <v>105035456</v>
       </c>
       <c r="B3" t="n">
-        <v>97335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222662</v>
+        <v>540</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Barkkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dicranum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sull. &amp; Lesq.) Lindb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väte, Skäldan, vägförgreningen 535 m SV, Rovalds 1:12 (2), Gtl</t>
+          <t>Slahagen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699433.9602591776</v>
+        <v>699486</v>
       </c>
       <c r="R3" t="n">
-        <v>6364033.843434261</v>
+        <v>6364003</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,95 +846,85 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80107493</v>
+        <v>105035426</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222322</v>
+        <v>737</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hejde, Skäldan, vägförgreningen 525 m SV, Forse 2:1 (2), Gtl</t>
+          <t>Slahagen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699453.9199261827</v>
+        <v>699473</v>
       </c>
       <c r="R4" t="n">
-        <v>6364024.016801195</v>
+        <v>6364060</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +968,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103911208</v>
+        <v>103911204</v>
       </c>
       <c r="B5" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699327.9325412875</v>
+        <v>699371</v>
       </c>
       <c r="R5" t="n">
-        <v>6364044.330370415</v>
+        <v>6364110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1052,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103911205</v>
+        <v>103911208</v>
       </c>
       <c r="B6" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699371.2545943954</v>
+        <v>699328</v>
       </c>
       <c r="R6" t="n">
-        <v>6364110.169501901</v>
+        <v>6364045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,19 +1153,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,16 +1189,11 @@
         <v>103912752</v>
       </c>
       <c r="B7" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1283,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699336.1545678433</v>
+        <v>699336</v>
       </c>
       <c r="R7" t="n">
-        <v>6364119.797515543</v>
+        <v>6364119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,19 +1254,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,50 +1292,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103911206</v>
+        <v>103912713</v>
       </c>
       <c r="B8" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248955</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hajdkvie N, Gtl</t>
+          <t>Hajdkvie Norr, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699327.9325412875</v>
+        <v>699308</v>
       </c>
       <c r="R8" t="n">
-        <v>6364044.330370415</v>
+        <v>6363974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,21 +1360,11 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1460,16 +1373,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1480,15 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103911209</v>
+        <v>105035444</v>
       </c>
       <c r="B9" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hajdkvie N, Gtl</t>
+          <t>Slahagen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699335.8524619738</v>
+        <v>699423</v>
       </c>
       <c r="R9" t="n">
-        <v>6363970.729563256</v>
+        <v>6364011</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,22 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,12 +1483,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1596,15 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103911204</v>
+        <v>80107496</v>
       </c>
       <c r="B10" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,34 +1510,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3674</v>
+        <v>221930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hajdkvie N, Gtl</t>
+          <t>Väte, Skäldan, vägförgreningen 535 m SV, Rovalds 1:12 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699371.2545943954</v>
+        <v>699434</v>
       </c>
       <c r="R10" t="n">
-        <v>6364110.169501901</v>
+        <v>6364034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,22 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,31 +1584,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103911207</v>
+        <v>80107493</v>
       </c>
       <c r="B11" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,34 +1607,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>222322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hajdkvie N, Gtl</t>
+          <t>Hejde, Skäldan, vägförgreningen 525 m SV, Forse 2:1 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699327.9325412875</v>
+        <v>699454</v>
       </c>
       <c r="R11" t="n">
-        <v>6364044.330370415</v>
+        <v>6364024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,22 +1661,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,66 +1681,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103912716</v>
+        <v>80107497</v>
       </c>
       <c r="B12" t="n">
-        <v>85129</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>427</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hajdkvie Norr, Gtl</t>
+          <t>Väte, Skäldan, vägförgreningen 535 m SV, Rovalds 1:12 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699332.6491381968</v>
+        <v>699434</v>
       </c>
       <c r="R12" t="n">
-        <v>6364080.743548909</v>
+        <v>6364034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,22 +1758,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,78 +1774,64 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103912722</v>
+        <v>105035447</v>
       </c>
       <c r="B13" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>229183</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Frostig asplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lecidella laureri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hepp) Körb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hajdkvie Norr, Gtl</t>
+          <t>Slahagen, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699315.9838717774</v>
+        <v>699507</v>
       </c>
       <c r="R13" t="n">
-        <v>6363967.599971931</v>
+        <v>6363992</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1855,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,21 +1871,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2070,15 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103912751</v>
+        <v>103911206</v>
       </c>
       <c r="B14" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,34 +1902,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hajdkvie Norr, Gtl</t>
+          <t>Hajdkvie N, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699332.2670454998</v>
+        <v>699328</v>
       </c>
       <c r="R14" t="n">
-        <v>6364077.484645513</v>
+        <v>6364045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,21 +1959,11 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2166,21 +1972,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2191,37 +1992,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103912713</v>
+        <v>103912751</v>
       </c>
       <c r="B15" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>248956</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2231,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699307.5447209227</v>
+        <v>699332</v>
       </c>
       <c r="R15" t="n">
-        <v>6363974.209010461</v>
+        <v>6364078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,19 +2060,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,53 +2098,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105035456</v>
+        <v>103911205</v>
       </c>
       <c r="B16" t="n">
-        <v>93295</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>540</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barkkvastmossa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum viride</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sull. &amp; Lesq.) Lindb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slahagen, Gtl</t>
+          <t>Hajdkvie N, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699485.2812606278</v>
+        <v>699371</v>
       </c>
       <c r="R16" t="n">
-        <v>6364002.32567435</v>
+        <v>6364110</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2382,43 +2163,32 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2429,53 +2199,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105035444</v>
+        <v>103911207</v>
       </c>
       <c r="B17" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slahagen, Gtl</t>
+          <t>Hajdkvie N, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699423.1887232976</v>
+        <v>699328</v>
       </c>
       <c r="R17" t="n">
-        <v>6364010.635428825</v>
+        <v>6364045</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,22 +2264,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,12 +2284,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2545,53 +2300,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105035447</v>
+        <v>103911209</v>
       </c>
       <c r="B18" t="n">
-        <v>77412</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229183</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Frostig asplav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lecidella laureri</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hepp) Körb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slahagen, Gtl</t>
+          <t>Hajdkvie N, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699506.3734922099</v>
+        <v>699336</v>
       </c>
       <c r="R18" t="n">
-        <v>6363991.474374466</v>
+        <v>6363970</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2615,22 +2365,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,15 +2385,121 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103912722</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hajdkvie Norr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>699316</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6363967</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog med inslag av gran och ek, frisk till fuktig mark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 44928-2022 artfynd.xlsx
+++ b/artfynd/A 44928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912716</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912752</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912713</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035444</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80107496</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80107493</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80107497</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035447</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911206</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912751</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911205</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911207</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2398,6 +2483,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911209</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2504,8 +2594,33 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912722</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>